--- a/password.xlsx
+++ b/password.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammed Al-Emara\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammed Al-Emara\Documents\GitHub\Statistical-notebook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D093896E-1301-4F63-A0C7-3CC13E1B98B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D90306-E7AA-45D9-8745-E072D437BED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>shakerkalaf</t>
   </si>
@@ -58,6 +58,15 @@
   </si>
   <si>
     <t>mohammed_alemara</t>
+  </si>
+  <si>
+    <t>سعد سجاد</t>
+  </si>
+  <si>
+    <t>saadsajjad</t>
+  </si>
+  <si>
+    <t>3E4BEC40F6</t>
   </si>
 </sst>
 </file>
@@ -375,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -427,6 +436,17 @@
         <v>6</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
